--- a/output/2026-09-24/enriched_analysis.xlsx
+++ b/output/2026-09-24/enriched_analysis.xlsx
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="V2" t="n">
-        <v>3.578</v>
+        <v>3.577</v>
       </c>
       <c r="W2" t="n">
-        <v>2960</v>
+        <v>2961</v>
       </c>
       <c r="X2" t="n">
         <v>23.2</v>
@@ -1164,10 +1164,10 @@
         <v>0.051</v>
       </c>
       <c r="W3" t="n">
-        <v>2622</v>
+        <v>2627</v>
       </c>
       <c r="X3" t="n">
-        <v>9.01</v>
+        <v>9.029999999999999</v>
       </c>
       <c r="Y3" t="n">
         <v>36</v>
@@ -1623,13 +1623,13 @@
         </is>
       </c>
       <c r="V5" t="n">
-        <v>0.974</v>
+        <v>0.951</v>
       </c>
       <c r="W5" t="n">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="X5" t="n">
-        <v>8.77</v>
+        <v>8.98</v>
       </c>
       <c r="Y5" t="n">
         <v>17</v>
@@ -1861,7 +1861,7 @@
         <v>320</v>
       </c>
       <c r="X6" t="n">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="Y6" t="n">
         <v>22</v>
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="V7" t="n">
-        <v>0.305</v>
+        <v>0.304</v>
       </c>
       <c r="W7" t="n">
-        <v>1004</v>
+        <v>1008</v>
       </c>
       <c r="X7" t="n">
-        <v>9.869999999999999</v>
+        <v>9.92</v>
       </c>
       <c r="Y7" t="n">
         <v>7</v>
@@ -2786,7 +2786,7 @@
         <v>0.382</v>
       </c>
       <c r="W10" t="n">
-        <v>2724</v>
+        <v>2723</v>
       </c>
       <c r="X10" t="n">
         <v>22.3</v>
@@ -3018,10 +3018,10 @@
         <v>0.044</v>
       </c>
       <c r="W11" t="n">
-        <v>16488</v>
+        <v>16526</v>
       </c>
       <c r="X11" t="n">
-        <v>42</v>
+        <v>42.1</v>
       </c>
       <c r="Y11" t="n">
         <v>83</v>
@@ -3250,7 +3250,7 @@
         <v>0.397</v>
       </c>
       <c r="W12" t="n">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="X12" t="n">
         <v>60.2</v>
@@ -3479,10 +3479,10 @@
         </is>
       </c>
       <c r="V13" t="n">
-        <v>1.572</v>
+        <v>1.585</v>
       </c>
       <c r="W13" t="n">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="X13" t="inlineStr"/>
       <c r="Y13" t="n">
@@ -3709,13 +3709,13 @@
         </is>
       </c>
       <c r="V14" t="n">
-        <v>0.163</v>
+        <v>0.159</v>
       </c>
       <c r="W14" t="n">
-        <v>678</v>
+        <v>698</v>
       </c>
       <c r="X14" t="n">
-        <v>56.7</v>
+        <v>58.3</v>
       </c>
       <c r="Y14" t="n">
         <v>3</v>
@@ -3941,13 +3941,13 @@
         </is>
       </c>
       <c r="V15" t="n">
-        <v>2.306</v>
+        <v>2.288</v>
       </c>
       <c r="W15" t="n">
-        <v>2584</v>
+        <v>2604</v>
       </c>
       <c r="X15" t="n">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Y15" t="n">
         <v>6</v>
@@ -4176,10 +4176,10 @@
         <v>0.098</v>
       </c>
       <c r="W16" t="n">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="X16" t="n">
-        <v>28</v>
+        <v>27.9</v>
       </c>
       <c r="Y16" t="n">
         <v>24</v>
@@ -4637,10 +4637,10 @@
         </is>
       </c>
       <c r="V18" t="n">
-        <v>2.823</v>
+        <v>2.827</v>
       </c>
       <c r="W18" t="n">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="X18" t="n">
         <v>26.2</v>
@@ -4866,7 +4866,7 @@
         <v>0.039</v>
       </c>
       <c r="W19" t="n">
-        <v>714</v>
+        <v>711</v>
       </c>
       <c r="X19" t="n">
         <v>11.6</v>
@@ -5095,13 +5095,13 @@
         </is>
       </c>
       <c r="V20" t="n">
-        <v>0.443</v>
+        <v>0.44</v>
       </c>
       <c r="W20" t="n">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="X20" t="n">
-        <v>38.9</v>
+        <v>39</v>
       </c>
       <c r="Y20" t="n">
         <v>21</v>
@@ -5330,10 +5330,10 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="W21" t="n">
-        <v>803</v>
+        <v>807</v>
       </c>
       <c r="X21" t="n">
-        <v>20.3</v>
+        <v>20.4</v>
       </c>
       <c r="Y21" t="n">
         <v>19</v>
@@ -5557,13 +5557,13 @@
         </is>
       </c>
       <c r="V22" t="n">
-        <v>0.293</v>
+        <v>0.296</v>
       </c>
       <c r="W22" t="n">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="X22" t="n">
-        <v>25.3</v>
+        <v>24.9</v>
       </c>
       <c r="Y22" t="n">
         <v>12</v>
@@ -5792,10 +5792,10 @@
         <v>0.134</v>
       </c>
       <c r="W23" t="n">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="X23" t="n">
-        <v>5.98</v>
+        <v>5.99</v>
       </c>
       <c r="Y23" t="n">
         <v>118</v>
@@ -5808,7 +5808,7 @@
         <v>1.03</v>
       </c>
       <c r="AC23" t="n">
-        <v>18.5</v>
+        <v>19.9</v>
       </c>
       <c r="AD23" t="n">
         <v>0.01</v>
@@ -6255,7 +6255,7 @@
         <v>380</v>
       </c>
       <c r="X25" t="n">
-        <v>1225</v>
+        <v>1227</v>
       </c>
       <c r="Y25" t="n">
         <v>-61</v>
@@ -6480,7 +6480,7 @@
         <v>0.038</v>
       </c>
       <c r="W26" t="n">
-        <v>3567</v>
+        <v>3569</v>
       </c>
       <c r="X26" t="n">
         <v>21.2</v>
@@ -6712,7 +6712,7 @@
         <v>0.024</v>
       </c>
       <c r="W27" t="n">
-        <v>1029</v>
+        <v>1039</v>
       </c>
       <c r="X27" t="inlineStr"/>
       <c r="Y27" t="n">
@@ -7174,7 +7174,7 @@
         <v>0.052</v>
       </c>
       <c r="W29" t="n">
-        <v>5035</v>
+        <v>5036</v>
       </c>
       <c r="X29" t="n">
         <v>32.8</v>
@@ -7406,7 +7406,7 @@
         <v>0.057</v>
       </c>
       <c r="W30" t="n">
-        <v>1937</v>
+        <v>1940</v>
       </c>
       <c r="X30" t="n">
         <v>44.5</v>
@@ -7638,7 +7638,7 @@
         <v>0.514</v>
       </c>
       <c r="W31" t="n">
-        <v>3763</v>
+        <v>3764</v>
       </c>
       <c r="X31" t="n">
         <v>26.3</v>
@@ -7867,10 +7867,10 @@
         </is>
       </c>
       <c r="V32" t="n">
-        <v>0.651</v>
+        <v>0.653</v>
       </c>
       <c r="W32" t="n">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="X32" t="n">
         <v>11.1</v>
@@ -8099,13 +8099,13 @@
         </is>
       </c>
       <c r="V33" t="n">
-        <v>0.096</v>
+        <v>0.095</v>
       </c>
       <c r="W33" t="n">
-        <v>1553</v>
+        <v>1557</v>
       </c>
       <c r="X33" t="n">
-        <v>14</v>
+        <v>14.1</v>
       </c>
       <c r="Y33" t="n">
         <v>6</v>
@@ -8331,13 +8331,13 @@
         </is>
       </c>
       <c r="V34" t="n">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="W34" t="n">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="X34" t="n">
-        <v>7.34</v>
+        <v>7.27</v>
       </c>
       <c r="Y34" t="n">
         <v>31</v>
@@ -9026,7 +9026,7 @@
         <v>0.021</v>
       </c>
       <c r="W37" t="n">
-        <v>9407</v>
+        <v>9416</v>
       </c>
       <c r="X37" t="n">
         <v>12.4</v>
@@ -9258,10 +9258,10 @@
         <v>0</v>
       </c>
       <c r="W38" t="n">
-        <v>3859</v>
+        <v>3849</v>
       </c>
       <c r="X38" t="n">
-        <v>86.90000000000001</v>
+        <v>86.59999999999999</v>
       </c>
       <c r="Y38" t="n">
         <v>42</v>
@@ -9954,10 +9954,10 @@
         <v>0</v>
       </c>
       <c r="W41" t="n">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="X41" t="n">
-        <v>11.5</v>
+        <v>11.4</v>
       </c>
       <c r="Y41" t="n">
         <v>5</v>
@@ -10183,13 +10183,13 @@
         </is>
       </c>
       <c r="V42" t="n">
-        <v>0.127</v>
+        <v>0.128</v>
       </c>
       <c r="W42" t="n">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="X42" t="n">
-        <v>13.9</v>
+        <v>13.8</v>
       </c>
       <c r="Y42" t="n">
         <v>61</v>
@@ -10413,13 +10413,13 @@
         </is>
       </c>
       <c r="V43" t="n">
-        <v>0.291</v>
+        <v>0.294</v>
       </c>
       <c r="W43" t="n">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="X43" t="n">
-        <v>15.2</v>
+        <v>15</v>
       </c>
       <c r="Y43" t="n">
         <v>16</v>
@@ -10645,13 +10645,13 @@
         </is>
       </c>
       <c r="V44" t="n">
-        <v>0.228</v>
+        <v>0.227</v>
       </c>
       <c r="W44" t="n">
-        <v>989</v>
+        <v>992</v>
       </c>
       <c r="X44" t="n">
-        <v>26.9</v>
+        <v>27</v>
       </c>
       <c r="Y44" t="n">
         <v>9</v>
@@ -11342,7 +11342,7 @@
         <v>0</v>
       </c>
       <c r="W47" t="n">
-        <v>9131</v>
+        <v>9142</v>
       </c>
       <c r="X47" t="n">
         <v>15.5</v>
@@ -11574,10 +11574,10 @@
         <v>0</v>
       </c>
       <c r="W48" t="n">
-        <v>120154</v>
+        <v>119891</v>
       </c>
       <c r="X48" t="n">
-        <v>34.6</v>
+        <v>34.5</v>
       </c>
       <c r="Y48" t="n">
         <v>18</v>
@@ -12035,13 +12035,13 @@
         </is>
       </c>
       <c r="V50" t="n">
-        <v>0.351</v>
+        <v>0.35</v>
       </c>
       <c r="W50" t="n">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="X50" t="n">
-        <v>98.7</v>
+        <v>99</v>
       </c>
       <c r="Y50" t="n">
         <v>246</v>
@@ -12270,7 +12270,7 @@
         <v>0.042</v>
       </c>
       <c r="W51" t="n">
-        <v>1635</v>
+        <v>1636</v>
       </c>
       <c r="X51" t="n">
         <v>21.4</v>
@@ -12502,7 +12502,7 @@
         <v>0.081</v>
       </c>
       <c r="W52" t="n">
-        <v>1688</v>
+        <v>1690</v>
       </c>
       <c r="X52" t="n">
         <v>30.5</v>

--- a/output/2026-09-24/enriched_analysis.xlsx
+++ b/output/2026-09-24/enriched_analysis.xlsx
@@ -445,7 +445,7 @@
     <col width="11" customWidth="1" min="13" max="13"/>
     <col width="18" customWidth="1" min="14" max="14"/>
     <col width="19" customWidth="1" min="15" max="15"/>
-    <col width="16" customWidth="1" min="16" max="16"/>
+    <col width="15" customWidth="1" min="16" max="16"/>
     <col width="19" customWidth="1" min="17" max="17"/>
     <col width="22" customWidth="1" min="18" max="18"/>
     <col width="22" customWidth="1" min="19" max="19"/>
@@ -889,25 +889,25 @@
         <v>89.12</v>
       </c>
       <c r="J2" t="n">
-        <v>74.89</v>
+        <v>75.34999999999999</v>
       </c>
       <c r="K2" t="n">
-        <v>19</v>
+        <v>18.3</v>
       </c>
       <c r="L2" t="n">
         <v>61.32</v>
       </c>
       <c r="M2" t="n">
-        <v>105.91</v>
+        <v>96.02</v>
       </c>
       <c r="N2" t="n">
-        <v>1059104595</v>
+        <v>960166595</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>1059104595</v>
+        <v>960166595</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
@@ -921,7 +921,7 @@
         <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
@@ -929,13 +929,13 @@
         </is>
       </c>
       <c r="V2" t="n">
-        <v>3.577</v>
+        <v>3.26</v>
       </c>
       <c r="W2" t="n">
-        <v>2961</v>
+        <v>2945</v>
       </c>
       <c r="X2" t="n">
-        <v>23.2</v>
+        <v>23</v>
       </c>
       <c r="Y2" t="n">
         <v>75</v>
@@ -971,10 +971,10 @@
         <v>144.6</v>
       </c>
       <c r="AJ2" t="n">
-        <v>74.11100190676549</v>
+        <v>74.69017219829051</v>
       </c>
       <c r="AK2" t="n">
-        <v>20.3</v>
+        <v>19.3</v>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
@@ -988,12 +988,12 @@
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>Late — Poor Entry</t>
+          <t>Mature — Wait for Pullback</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>19-06-2026</t>
+          <t>24-06-2026</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
@@ -1002,10 +1002,10 @@
         </is>
       </c>
       <c r="AQ2" t="n">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="AR2" t="n">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="AS2" t="n">
         <v>15</v>
@@ -1164,10 +1164,10 @@
         <v>0.051</v>
       </c>
       <c r="W3" t="n">
-        <v>2627</v>
+        <v>2603</v>
       </c>
       <c r="X3" t="n">
-        <v>9.029999999999999</v>
+        <v>8.93</v>
       </c>
       <c r="Y3" t="n">
         <v>36</v>
@@ -1393,10 +1393,10 @@
         </is>
       </c>
       <c r="V4" t="n">
-        <v>0.907</v>
+        <v>0.91</v>
       </c>
       <c r="W4" t="n">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="X4" t="inlineStr"/>
       <c r="Y4" t="n">
@@ -1623,13 +1623,13 @@
         </is>
       </c>
       <c r="V5" t="n">
-        <v>0.951</v>
+        <v>0.947</v>
       </c>
       <c r="W5" t="n">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="X5" t="n">
-        <v>8.98</v>
+        <v>9.01</v>
       </c>
       <c r="Y5" t="n">
         <v>17</v>
@@ -1855,13 +1855,13 @@
         </is>
       </c>
       <c r="V6" t="n">
-        <v>0.5639999999999999</v>
+        <v>0.552</v>
       </c>
       <c r="W6" t="n">
-        <v>320</v>
+        <v>327</v>
       </c>
       <c r="X6" t="n">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="Y6" t="n">
         <v>22</v>
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="V7" t="n">
-        <v>0.304</v>
+        <v>0.307</v>
       </c>
       <c r="W7" t="n">
-        <v>1008</v>
+        <v>999</v>
       </c>
       <c r="X7" t="n">
-        <v>9.92</v>
+        <v>9.83</v>
       </c>
       <c r="Y7" t="n">
         <v>7</v>
@@ -2319,13 +2319,13 @@
         </is>
       </c>
       <c r="V8" t="n">
-        <v>0.12</v>
+        <v>0.115</v>
       </c>
       <c r="W8" t="n">
-        <v>2611</v>
+        <v>2729</v>
       </c>
       <c r="X8" t="n">
-        <v>22.9</v>
+        <v>23.9</v>
       </c>
       <c r="Y8" t="n">
         <v>-3</v>
@@ -2551,13 +2551,13 @@
         </is>
       </c>
       <c r="V9" t="n">
-        <v>0.054</v>
+        <v>0.056</v>
       </c>
       <c r="W9" t="n">
-        <v>1535</v>
+        <v>1476</v>
       </c>
       <c r="X9" t="n">
-        <v>20.7</v>
+        <v>19.9</v>
       </c>
       <c r="Y9" t="n">
         <v>55</v>
@@ -2783,13 +2783,13 @@
         </is>
       </c>
       <c r="V10" t="n">
-        <v>0.382</v>
+        <v>0.381</v>
       </c>
       <c r="W10" t="n">
-        <v>2723</v>
+        <v>2732</v>
       </c>
       <c r="X10" t="n">
-        <v>22.3</v>
+        <v>22.4</v>
       </c>
       <c r="Y10" t="n">
         <v>8</v>
@@ -3018,10 +3018,10 @@
         <v>0.044</v>
       </c>
       <c r="W11" t="n">
-        <v>16526</v>
+        <v>16283</v>
       </c>
       <c r="X11" t="n">
-        <v>42.1</v>
+        <v>41.5</v>
       </c>
       <c r="Y11" t="n">
         <v>83</v>
@@ -3247,13 +3247,13 @@
         </is>
       </c>
       <c r="V12" t="n">
-        <v>0.397</v>
+        <v>0.384</v>
       </c>
       <c r="W12" t="n">
-        <v>1182</v>
+        <v>1222</v>
       </c>
       <c r="X12" t="n">
-        <v>60.2</v>
+        <v>62.3</v>
       </c>
       <c r="Y12" t="n">
         <v>21</v>
@@ -3479,10 +3479,10 @@
         </is>
       </c>
       <c r="V13" t="n">
-        <v>1.585</v>
+        <v>1.623</v>
       </c>
       <c r="W13" t="n">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="X13" t="inlineStr"/>
       <c r="Y13" t="n">
@@ -3709,13 +3709,13 @@
         </is>
       </c>
       <c r="V14" t="n">
-        <v>0.159</v>
+        <v>0.164</v>
       </c>
       <c r="W14" t="n">
-        <v>698</v>
+        <v>676</v>
       </c>
       <c r="X14" t="n">
-        <v>58.3</v>
+        <v>56.5</v>
       </c>
       <c r="Y14" t="n">
         <v>3</v>
@@ -3941,13 +3941,13 @@
         </is>
       </c>
       <c r="V15" t="n">
-        <v>2.288</v>
+        <v>2.306</v>
       </c>
       <c r="W15" t="n">
-        <v>2604</v>
+        <v>2584</v>
       </c>
       <c r="X15" t="n">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="Y15" t="n">
         <v>6</v>
@@ -4176,10 +4176,10 @@
         <v>0.098</v>
       </c>
       <c r="W16" t="n">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="X16" t="n">
-        <v>27.9</v>
+        <v>28.1</v>
       </c>
       <c r="Y16" t="n">
         <v>24</v>
@@ -4405,13 +4405,13 @@
         </is>
       </c>
       <c r="V17" t="n">
-        <v>0.075</v>
+        <v>0.076</v>
       </c>
       <c r="W17" t="n">
-        <v>451</v>
+        <v>444</v>
       </c>
       <c r="X17" t="n">
-        <v>13.3</v>
+        <v>13.1</v>
       </c>
       <c r="Y17" t="n">
         <v>-8</v>
@@ -4637,13 +4637,13 @@
         </is>
       </c>
       <c r="V18" t="n">
-        <v>2.827</v>
+        <v>2.811</v>
       </c>
       <c r="W18" t="n">
-        <v>696</v>
+        <v>700</v>
       </c>
       <c r="X18" t="n">
-        <v>26.2</v>
+        <v>26.3</v>
       </c>
       <c r="Y18" t="n">
         <v>30</v>
@@ -4863,13 +4863,13 @@
         </is>
       </c>
       <c r="V19" t="n">
-        <v>0.039</v>
+        <v>0.04</v>
       </c>
       <c r="W19" t="n">
-        <v>711</v>
+        <v>694</v>
       </c>
       <c r="X19" t="n">
-        <v>11.6</v>
+        <v>11.3</v>
       </c>
       <c r="Y19" t="n">
         <v>-5</v>
@@ -5095,13 +5095,13 @@
         </is>
       </c>
       <c r="V20" t="n">
-        <v>0.44</v>
+        <v>0.438</v>
       </c>
       <c r="W20" t="n">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="X20" t="n">
-        <v>39</v>
+        <v>39.2</v>
       </c>
       <c r="Y20" t="n">
         <v>21</v>
@@ -5330,10 +5330,10 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="W21" t="n">
-        <v>807</v>
+        <v>810</v>
       </c>
       <c r="X21" t="n">
-        <v>20.4</v>
+        <v>20.5</v>
       </c>
       <c r="Y21" t="n">
         <v>19</v>
@@ -5557,13 +5557,13 @@
         </is>
       </c>
       <c r="V22" t="n">
-        <v>0.296</v>
+        <v>0.29</v>
       </c>
       <c r="W22" t="n">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="X22" t="n">
-        <v>24.9</v>
+        <v>25.5</v>
       </c>
       <c r="Y22" t="n">
         <v>12</v>
@@ -5792,10 +5792,10 @@
         <v>0.134</v>
       </c>
       <c r="W23" t="n">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="X23" t="n">
-        <v>5.99</v>
+        <v>5.96</v>
       </c>
       <c r="Y23" t="n">
         <v>118</v>
@@ -6020,10 +6020,10 @@
         <v>0.007</v>
       </c>
       <c r="W24" t="n">
-        <v>5610</v>
+        <v>5529</v>
       </c>
       <c r="X24" t="n">
-        <v>9.48</v>
+        <v>9.34</v>
       </c>
       <c r="Y24" t="n">
         <v>43</v>
@@ -6249,13 +6249,13 @@
         </is>
       </c>
       <c r="V25" t="n">
-        <v>0.618</v>
+        <v>0.627</v>
       </c>
       <c r="W25" t="n">
-        <v>380</v>
+        <v>374</v>
       </c>
       <c r="X25" t="n">
-        <v>1227</v>
+        <v>1208</v>
       </c>
       <c r="Y25" t="n">
         <v>-61</v>
@@ -6480,10 +6480,10 @@
         <v>0.038</v>
       </c>
       <c r="W26" t="n">
-        <v>3569</v>
+        <v>3540</v>
       </c>
       <c r="X26" t="n">
-        <v>21.2</v>
+        <v>21</v>
       </c>
       <c r="Y26" t="n">
         <v>-4</v>
@@ -6712,7 +6712,7 @@
         <v>0.024</v>
       </c>
       <c r="W27" t="n">
-        <v>1039</v>
+        <v>1012</v>
       </c>
       <c r="X27" t="inlineStr"/>
       <c r="Y27" t="n">
@@ -6942,7 +6942,7 @@
         <v>0.036</v>
       </c>
       <c r="W28" t="n">
-        <v>1148</v>
+        <v>1155</v>
       </c>
       <c r="X28" t="n">
         <v>123</v>
@@ -7174,10 +7174,10 @@
         <v>0.052</v>
       </c>
       <c r="W29" t="n">
-        <v>5036</v>
+        <v>5012</v>
       </c>
       <c r="X29" t="n">
-        <v>32.8</v>
+        <v>32.7</v>
       </c>
       <c r="Y29" t="n">
         <v>-25</v>
@@ -7406,10 +7406,10 @@
         <v>0.057</v>
       </c>
       <c r="W30" t="n">
-        <v>1940</v>
+        <v>1922</v>
       </c>
       <c r="X30" t="n">
-        <v>44.5</v>
+        <v>44.1</v>
       </c>
       <c r="Y30" t="n">
         <v>20</v>
@@ -7635,13 +7635,13 @@
         </is>
       </c>
       <c r="V31" t="n">
-        <v>0.514</v>
+        <v>0.526</v>
       </c>
       <c r="W31" t="n">
-        <v>3764</v>
+        <v>3677</v>
       </c>
       <c r="X31" t="n">
-        <v>26.3</v>
+        <v>25.7</v>
       </c>
       <c r="Y31" t="n">
         <v>2</v>
@@ -7867,13 +7867,13 @@
         </is>
       </c>
       <c r="V32" t="n">
-        <v>0.653</v>
+        <v>0.656</v>
       </c>
       <c r="W32" t="n">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="X32" t="n">
-        <v>11.1</v>
+        <v>11</v>
       </c>
       <c r="Y32" t="n">
         <v>19</v>
@@ -8099,13 +8099,13 @@
         </is>
       </c>
       <c r="V33" t="n">
-        <v>0.095</v>
+        <v>0.097</v>
       </c>
       <c r="W33" t="n">
-        <v>1557</v>
+        <v>1537</v>
       </c>
       <c r="X33" t="n">
-        <v>14.1</v>
+        <v>13.9</v>
       </c>
       <c r="Y33" t="n">
         <v>6</v>
@@ -8331,13 +8331,13 @@
         </is>
       </c>
       <c r="V34" t="n">
-        <v>0.8</v>
+        <v>0.83</v>
       </c>
       <c r="W34" t="n">
-        <v>248</v>
+        <v>239</v>
       </c>
       <c r="X34" t="n">
-        <v>7.27</v>
+        <v>7.01</v>
       </c>
       <c r="Y34" t="n">
         <v>31</v>
@@ -8559,13 +8559,13 @@
         </is>
       </c>
       <c r="V35" t="n">
-        <v>0.193</v>
+        <v>0.196</v>
       </c>
       <c r="W35" t="n">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="X35" t="n">
-        <v>35.9</v>
+        <v>35.2</v>
       </c>
       <c r="Y35" t="n">
         <v>-44</v>
@@ -8794,10 +8794,10 @@
         <v>0.008999999999999999</v>
       </c>
       <c r="W36" t="n">
-        <v>53607</v>
+        <v>53129</v>
       </c>
       <c r="X36" t="n">
-        <v>45.4</v>
+        <v>45</v>
       </c>
       <c r="Y36" t="n">
         <v>5</v>
@@ -9023,13 +9023,13 @@
         </is>
       </c>
       <c r="V37" t="n">
-        <v>0.021</v>
+        <v>0.02</v>
       </c>
       <c r="W37" t="n">
-        <v>9416</v>
+        <v>9533</v>
       </c>
       <c r="X37" t="n">
-        <v>12.4</v>
+        <v>12.6</v>
       </c>
       <c r="Y37" t="n">
         <v>-12</v>
@@ -9258,10 +9258,10 @@
         <v>0</v>
       </c>
       <c r="W38" t="n">
-        <v>3849</v>
+        <v>3771</v>
       </c>
       <c r="X38" t="n">
-        <v>86.59999999999999</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="Y38" t="n">
         <v>42</v>
@@ -9487,13 +9487,13 @@
         </is>
       </c>
       <c r="V39" t="n">
-        <v>0.361</v>
+        <v>0.359</v>
       </c>
       <c r="W39" t="n">
-        <v>665</v>
+        <v>668</v>
       </c>
       <c r="X39" t="n">
-        <v>14.6</v>
+        <v>14.7</v>
       </c>
       <c r="Y39" t="n">
         <v>-1</v>
@@ -9719,13 +9719,13 @@
         </is>
       </c>
       <c r="V40" t="n">
-        <v>0.209</v>
+        <v>0.205</v>
       </c>
       <c r="W40" t="n">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="X40" t="n">
-        <v>25.6</v>
+        <v>26.1</v>
       </c>
       <c r="Y40" t="n">
         <v>21</v>
@@ -9954,10 +9954,10 @@
         <v>0</v>
       </c>
       <c r="W41" t="n">
-        <v>487</v>
+        <v>503</v>
       </c>
       <c r="X41" t="n">
-        <v>11.4</v>
+        <v>11.8</v>
       </c>
       <c r="Y41" t="n">
         <v>5</v>
@@ -10183,13 +10183,13 @@
         </is>
       </c>
       <c r="V42" t="n">
-        <v>0.128</v>
+        <v>0.13</v>
       </c>
       <c r="W42" t="n">
-        <v>584</v>
+        <v>575</v>
       </c>
       <c r="X42" t="n">
-        <v>13.8</v>
+        <v>13.7</v>
       </c>
       <c r="Y42" t="n">
         <v>61</v>
@@ -10413,13 +10413,13 @@
         </is>
       </c>
       <c r="V43" t="n">
-        <v>0.294</v>
+        <v>0.299</v>
       </c>
       <c r="W43" t="n">
-        <v>284</v>
+        <v>279</v>
       </c>
       <c r="X43" t="n">
-        <v>15</v>
+        <v>14.7</v>
       </c>
       <c r="Y43" t="n">
         <v>16</v>
@@ -10645,13 +10645,13 @@
         </is>
       </c>
       <c r="V44" t="n">
-        <v>0.227</v>
+        <v>0.229</v>
       </c>
       <c r="W44" t="n">
-        <v>992</v>
+        <v>986</v>
       </c>
       <c r="X44" t="n">
-        <v>27</v>
+        <v>26.8</v>
       </c>
       <c r="Y44" t="n">
         <v>9</v>
@@ -10877,13 +10877,13 @@
         </is>
       </c>
       <c r="V45" t="n">
-        <v>0.073</v>
+        <v>0.074</v>
       </c>
       <c r="W45" t="n">
-        <v>734</v>
+        <v>727</v>
       </c>
       <c r="X45" t="n">
-        <v>13.3</v>
+        <v>13.2</v>
       </c>
       <c r="Y45" t="n">
         <v>185</v>
@@ -11107,13 +11107,13 @@
         </is>
       </c>
       <c r="V46" t="n">
-        <v>0.22</v>
+        <v>0.222</v>
       </c>
       <c r="W46" t="n">
-        <v>1810</v>
+        <v>1794</v>
       </c>
       <c r="X46" t="n">
-        <v>19.2</v>
+        <v>19</v>
       </c>
       <c r="Y46" t="n">
         <v>-3</v>
@@ -11342,10 +11342,10 @@
         <v>0</v>
       </c>
       <c r="W47" t="n">
-        <v>9142</v>
+        <v>8969</v>
       </c>
       <c r="X47" t="n">
-        <v>15.5</v>
+        <v>15.2</v>
       </c>
       <c r="Y47" t="n">
         <v>21</v>
@@ -11574,10 +11574,10 @@
         <v>0</v>
       </c>
       <c r="W48" t="n">
-        <v>119891</v>
+        <v>118840</v>
       </c>
       <c r="X48" t="n">
-        <v>34.5</v>
+        <v>34.2</v>
       </c>
       <c r="Y48" t="n">
         <v>18</v>
@@ -11806,10 +11806,10 @@
         <v>0</v>
       </c>
       <c r="W49" t="n">
-        <v>2563</v>
+        <v>2819</v>
       </c>
       <c r="X49" t="n">
-        <v>758</v>
+        <v>834</v>
       </c>
       <c r="Y49" t="n">
         <v>3</v>
@@ -12035,13 +12035,13 @@
         </is>
       </c>
       <c r="V50" t="n">
-        <v>0.35</v>
+        <v>0.352</v>
       </c>
       <c r="W50" t="n">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="X50" t="n">
-        <v>99</v>
+        <v>98.5</v>
       </c>
       <c r="Y50" t="n">
         <v>246</v>
@@ -12267,13 +12267,13 @@
         </is>
       </c>
       <c r="V51" t="n">
-        <v>0.042</v>
+        <v>0.043</v>
       </c>
       <c r="W51" t="n">
-        <v>1636</v>
+        <v>1629</v>
       </c>
       <c r="X51" t="n">
-        <v>21.4</v>
+        <v>21.3</v>
       </c>
       <c r="Y51" t="n">
         <v>10</v>
@@ -12499,13 +12499,13 @@
         </is>
       </c>
       <c r="V52" t="n">
-        <v>0.081</v>
+        <v>0.083</v>
       </c>
       <c r="W52" t="n">
-        <v>1690</v>
+        <v>1658</v>
       </c>
       <c r="X52" t="n">
-        <v>30.5</v>
+        <v>30</v>
       </c>
       <c r="Y52" t="n">
         <v>39</v>
@@ -12743,19 +12743,19 @@
         <v>89.12</v>
       </c>
       <c r="D2" t="n">
-        <v>74.89</v>
+        <v>75.34999999999999</v>
       </c>
       <c r="E2" t="n">
-        <v>19</v>
+        <v>18.3</v>
       </c>
       <c r="F2" t="n">
         <v>61.32</v>
       </c>
       <c r="G2" t="n">
-        <v>105.91</v>
+        <v>96.02</v>
       </c>
       <c r="H2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>

--- a/output/2026-09-24/enriched_analysis.xlsx
+++ b/output/2026-09-24/enriched_analysis.xlsx
@@ -929,13 +929,13 @@
         </is>
       </c>
       <c r="V2" t="n">
-        <v>3.324</v>
+        <v>3.353</v>
       </c>
       <c r="W2" t="n">
-        <v>2889</v>
+        <v>2864</v>
       </c>
       <c r="X2" t="n">
-        <v>22.6</v>
+        <v>22.4</v>
       </c>
       <c r="Y2" t="n">
         <v>75</v>
@@ -1121,25 +1121,25 @@
         <v>998.35</v>
       </c>
       <c r="J3" t="n">
-        <v>776.36</v>
+        <v>782.48</v>
       </c>
       <c r="K3" t="n">
-        <v>28.6</v>
+        <v>27.6</v>
       </c>
       <c r="L3" t="n">
         <v>61.71</v>
       </c>
       <c r="M3" t="n">
-        <v>2.78</v>
+        <v>2.88</v>
       </c>
       <c r="N3" t="n">
-        <v>27759467</v>
+        <v>28765495</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>27759467</v>
+        <v>28765495</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -1153,15 +1153,15 @@
         <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>21-09-2026</t>
+          <t>22-09-2026</t>
         </is>
       </c>
       <c r="V3" t="n">
-        <v>0.898</v>
+        <v>0.931</v>
       </c>
       <c r="W3" t="n">
         <v>309</v>
@@ -1201,10 +1201,10 @@
         <v>28</v>
       </c>
       <c r="AJ3" t="n">
-        <v>759.6490229599013</v>
+        <v>764.770506385412</v>
       </c>
       <c r="AK3" t="n">
-        <v>31.4</v>
+        <v>30.5</v>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
@@ -1228,47 +1228,47 @@
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>21-09-2026</t>
+          <t>22-09-2026</t>
         </is>
       </c>
       <c r="AQ3" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="AR3" t="n">
         <v>38</v>
       </c>
       <c r="AS3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV3" t="n">
         <v>3</v>
       </c>
-      <c r="AT3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>2</v>
-      </c>
       <c r="AW3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AX3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AY3" t="n">
-        <v>6467878</v>
+        <v>7473906</v>
       </c>
       <c r="AZ3" t="n">
-        <v>6467878</v>
+        <v>7473906</v>
       </c>
       <c r="BA3" t="n">
-        <v>11642564</v>
+        <v>12648592</v>
       </c>
       <c r="BB3" t="n">
-        <v>35104141</v>
+        <v>36110169</v>
       </c>
       <c r="BC3" t="n">
-        <v>35104141</v>
+        <v>36110169</v>
       </c>
       <c r="BD3" t="n">
         <v>0</v>
@@ -1301,10 +1301,10 @@
         <v>0</v>
       </c>
       <c r="BN3" t="n">
-        <v>6467878</v>
+        <v>7473906</v>
       </c>
       <c r="BO3" t="n">
-        <v>11642564</v>
+        <v>12648592</v>
       </c>
       <c r="BP3" t="n">
         <v>1</v>
@@ -1313,7 +1313,7 @@
         <v>0</v>
       </c>
       <c r="BR3" t="n">
-        <v>0.5555</v>
+        <v>0.5909</v>
       </c>
     </row>
     <row r="4">
@@ -1391,13 +1391,13 @@
         </is>
       </c>
       <c r="V4" t="n">
-        <v>0.979</v>
+        <v>0.969</v>
       </c>
       <c r="W4" t="n">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="X4" t="n">
-        <v>8.73</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Y4" t="n">
         <v>17</v>
@@ -1412,7 +1412,7 @@
         <v>2.73</v>
       </c>
       <c r="AC4" t="n">
-        <v>13.7</v>
+        <v>13.6</v>
       </c>
       <c r="AD4" t="n">
         <v>1.86</v>
@@ -1858,10 +1858,10 @@
         <v>0.052</v>
       </c>
       <c r="W6" t="n">
-        <v>1580</v>
+        <v>1578</v>
       </c>
       <c r="X6" t="n">
-        <v>21.3</v>
+        <v>21.2</v>
       </c>
       <c r="Y6" t="n">
         <v>55</v>
@@ -2322,10 +2322,10 @@
         <v>0.118</v>
       </c>
       <c r="W8" t="n">
-        <v>2650</v>
+        <v>2655</v>
       </c>
       <c r="X8" t="n">
-        <v>23.2</v>
+        <v>23.3</v>
       </c>
       <c r="Y8" t="n">
         <v>-3</v>
@@ -2554,7 +2554,7 @@
         <v>0.295</v>
       </c>
       <c r="W9" t="n">
-        <v>1038</v>
+        <v>1039</v>
       </c>
       <c r="X9" t="n">
         <v>10.2</v>
@@ -3248,7 +3248,7 @@
         <v>0.045</v>
       </c>
       <c r="W12" t="n">
-        <v>15872</v>
+        <v>15865</v>
       </c>
       <c r="X12" t="n">
         <v>40.4</v>
@@ -4176,7 +4176,7 @@
         <v>0.074</v>
       </c>
       <c r="W16" t="n">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="X16" t="n">
         <v>13.5</v>
@@ -4411,7 +4411,7 @@
         <v>261</v>
       </c>
       <c r="X17" t="n">
-        <v>28</v>
+        <v>27.9</v>
       </c>
       <c r="Y17" t="n">
         <v>24</v>
@@ -5021,16 +5021,16 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>AFFORDABLE</t>
+          <t>TAINWALCHM</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>AFFORDABLE ROBOTIC &amp; AUTOMATION LIMITED</t>
+          <t>TAINWALA CHEMICALS AND PLASTICS (INDIA) LIMITED</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -5041,37 +5041,37 @@
         <v>8</v>
       </c>
       <c r="F20" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="G20" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="H20" t="n">
         <v>-1</v>
       </c>
       <c r="I20" t="n">
-        <v>177.35</v>
+        <v>216.79</v>
       </c>
       <c r="J20" t="n">
-        <v>166.77</v>
+        <v>210</v>
       </c>
       <c r="K20" t="n">
-        <v>6.3</v>
+        <v>3.2</v>
       </c>
       <c r="L20" t="n">
-        <v>61.48</v>
+        <v>67.04000000000001</v>
       </c>
       <c r="M20" t="n">
-        <v>0.4</v>
+        <v>0.59</v>
       </c>
       <c r="N20" t="n">
-        <v>3987724</v>
+        <v>5944992</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>3987724</v>
+        <v>5944992</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
@@ -5085,60 +5085,60 @@
         <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>18-09-2026</t>
+          <t>17-09-2026</t>
         </is>
       </c>
       <c r="V20" t="n">
-        <v>0.191</v>
+        <v>0.291</v>
       </c>
       <c r="W20" t="n">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="X20" t="n">
-        <v>36.2</v>
+        <v>25.3</v>
       </c>
       <c r="Y20" t="n">
-        <v>-44</v>
+        <v>12</v>
       </c>
       <c r="Z20" t="n">
-        <v>-3.28</v>
+        <v>0.03</v>
       </c>
       <c r="AA20" t="n">
-        <v>141</v>
+        <v>16</v>
       </c>
       <c r="AB20" t="n">
-        <v>-4.05</v>
+        <v>0.03</v>
       </c>
       <c r="AC20" t="n">
-        <v>8.25</v>
+        <v>7.91</v>
       </c>
       <c r="AD20" t="n">
-        <v>0.44</v>
+        <v>0</v>
       </c>
       <c r="AE20" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF20" t="n">
-        <v>-35.96</v>
+        <v>3.16</v>
       </c>
       <c r="AG20" t="n">
-        <v>175.12</v>
+        <v>209.69</v>
       </c>
       <c r="AH20" t="n">
-        <v>179.25</v>
+        <v>196.32</v>
       </c>
       <c r="AI20" t="n">
-        <v>24.8</v>
+        <v>19.5</v>
       </c>
       <c r="AJ20" t="n">
-        <v>166.7666443626631</v>
+        <v>210.0036030944223</v>
       </c>
       <c r="AK20" t="n">
-        <v>6.3</v>
+        <v>3.2</v>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
@@ -5147,62 +5147,62 @@
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>Early Accumulation</t>
+          <t>Confirmed Accumulation</t>
         </is>
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>Early Accumulation</t>
+          <t>Confirmed Accumulation</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>16-09-2026</t>
+          <t>18-08-2026</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>18-09-2026</t>
+          <t>17-09-2026</t>
         </is>
       </c>
       <c r="AQ20" t="n">
-        <v>2</v>
+        <v>30</v>
       </c>
       <c r="AR20" t="n">
-        <v>8</v>
+        <v>37</v>
       </c>
       <c r="AS20" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AT20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU20" t="n">
         <v>4</v>
       </c>
       <c r="AV20" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="AW20" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="AX20" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="AY20" t="n">
-        <v>2328713</v>
+        <v>0</v>
       </c>
       <c r="AZ20" t="n">
-        <v>3987724</v>
+        <v>2295648</v>
       </c>
       <c r="BA20" t="n">
-        <v>3987724</v>
+        <v>3513481</v>
       </c>
       <c r="BB20" t="n">
-        <v>3987724</v>
+        <v>5944992</v>
       </c>
       <c r="BC20" t="n">
-        <v>3987724</v>
+        <v>5944992</v>
       </c>
       <c r="BD20" t="n">
         <v>0</v>
@@ -5235,10 +5235,10 @@
         <v>0</v>
       </c>
       <c r="BN20" t="n">
-        <v>2328713</v>
+        <v>0</v>
       </c>
       <c r="BO20" t="n">
-        <v>3987724</v>
+        <v>3513481</v>
       </c>
       <c r="BP20" t="n">
         <v>1</v>
@@ -5247,22 +5247,22 @@
         <v>0</v>
       </c>
       <c r="BR20" t="n">
-        <v>0.584</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>TAINWALCHM</t>
+          <t>AFFORDABLE</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>TAINWALA CHEMICALS AND PLASTICS (INDIA) LIMITED</t>
+          <t>AFFORDABLE ROBOTIC &amp; AUTOMATION LIMITED</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -5270,40 +5270,40 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F21" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="G21" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="H21" t="n">
         <v>-1</v>
       </c>
       <c r="I21" t="n">
-        <v>216.79</v>
+        <v>177.35</v>
       </c>
       <c r="J21" t="n">
-        <v>210</v>
+        <v>169.88</v>
       </c>
       <c r="K21" t="n">
-        <v>3.2</v>
+        <v>4.4</v>
       </c>
       <c r="L21" t="n">
-        <v>67.04000000000001</v>
+        <v>61.48</v>
       </c>
       <c r="M21" t="n">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="N21" t="n">
-        <v>5944992</v>
+        <v>5988193</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>5944992</v>
+        <v>5988193</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
@@ -5317,60 +5317,60 @@
         <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>17-09-2026</t>
+          <t>23-09-2026</t>
         </is>
       </c>
       <c r="V21" t="n">
-        <v>0.291</v>
+        <v>0.287</v>
       </c>
       <c r="W21" t="n">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="X21" t="n">
-        <v>25.3</v>
+        <v>36.2</v>
       </c>
       <c r="Y21" t="n">
-        <v>12</v>
+        <v>-44</v>
       </c>
       <c r="Z21" t="n">
-        <v>0.03</v>
+        <v>-3.28</v>
       </c>
       <c r="AA21" t="n">
-        <v>16</v>
+        <v>141</v>
       </c>
       <c r="AB21" t="n">
-        <v>0.03</v>
+        <v>-4.05</v>
       </c>
       <c r="AC21" t="n">
-        <v>7.91</v>
+        <v>8.25</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>0.44</v>
       </c>
       <c r="AE21" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF21" t="n">
-        <v>3.16</v>
+        <v>-35.96</v>
       </c>
       <c r="AG21" t="n">
-        <v>209.69</v>
+        <v>175.12</v>
       </c>
       <c r="AH21" t="n">
-        <v>196.32</v>
+        <v>179.25</v>
       </c>
       <c r="AI21" t="n">
-        <v>19.5</v>
+        <v>24.8</v>
       </c>
       <c r="AJ21" t="n">
-        <v>210.0036030944223</v>
+        <v>169.8778156028369</v>
       </c>
       <c r="AK21" t="n">
-        <v>3.2</v>
+        <v>4.4</v>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
@@ -5379,62 +5379,62 @@
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>Confirmed Accumulation</t>
+          <t>Early Accumulation</t>
         </is>
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>Confirmed Accumulation</t>
+          <t>Early Accumulation</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>18-08-2026</t>
+          <t>16-09-2026</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>17-09-2026</t>
+          <t>23-09-2026</t>
         </is>
       </c>
       <c r="AQ21" t="n">
-        <v>30</v>
+        <v>7</v>
       </c>
       <c r="AR21" t="n">
-        <v>37</v>
+        <v>8</v>
       </c>
       <c r="AS21" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="AT21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU21" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AV21" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="AW21" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="AX21" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="AY21" t="n">
-        <v>0</v>
+        <v>4329182</v>
       </c>
       <c r="AZ21" t="n">
-        <v>2295648</v>
+        <v>5988193</v>
       </c>
       <c r="BA21" t="n">
-        <v>3513481</v>
+        <v>5988193</v>
       </c>
       <c r="BB21" t="n">
-        <v>5944992</v>
+        <v>5988193</v>
       </c>
       <c r="BC21" t="n">
-        <v>5944992</v>
+        <v>5988193</v>
       </c>
       <c r="BD21" t="n">
         <v>0</v>
@@ -5467,10 +5467,10 @@
         <v>0</v>
       </c>
       <c r="BN21" t="n">
-        <v>0</v>
+        <v>4329182</v>
       </c>
       <c r="BO21" t="n">
-        <v>3513481</v>
+        <v>5988193</v>
       </c>
       <c r="BP21" t="n">
         <v>1</v>
@@ -5479,7 +5479,7 @@
         <v>0</v>
       </c>
       <c r="BR21" t="n">
-        <v>0</v>
+        <v>0.723</v>
       </c>
     </row>
     <row r="22">
@@ -5949,12 +5949,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>JAYAGROGN</t>
+          <t>SGIL</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Jayant Agro-Organics Limited</t>
+          <t>SYNERGY GREEN INDUSTRIES LIMITED</t>
         </is>
       </c>
       <c r="C24" t="n">
@@ -5966,40 +5966,40 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F24" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="G24" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="H24" t="n">
         <v>0</v>
       </c>
       <c r="I24" t="n">
-        <v>230.91</v>
+        <v>646.6</v>
       </c>
       <c r="J24" t="n">
-        <v>234.37</v>
+        <v>593.62</v>
       </c>
       <c r="K24" t="n">
-        <v>-1.5</v>
+        <v>8.9</v>
       </c>
       <c r="L24" t="n">
-        <v>67.13</v>
+        <v>74.02</v>
       </c>
       <c r="M24" t="n">
-        <v>0.28</v>
+        <v>0.25</v>
       </c>
       <c r="N24" t="n">
-        <v>2770203</v>
+        <v>2458195</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>2770203</v>
+        <v>2458195</v>
       </c>
       <c r="Q24" t="n">
         <v>0</v>
@@ -6013,124 +6013,122 @@
         <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>22-09-2026</t>
+          <t>11-09-2026</t>
         </is>
       </c>
       <c r="V24" t="n">
-        <v>0.04</v>
+        <v>0.025</v>
       </c>
       <c r="W24" t="n">
-        <v>687</v>
-      </c>
-      <c r="X24" t="n">
-        <v>11.2</v>
-      </c>
+        <v>1003</v>
+      </c>
+      <c r="X24" t="inlineStr"/>
       <c r="Y24" t="n">
-        <v>-5</v>
+        <v>-2</v>
       </c>
       <c r="Z24" t="n">
-        <v>32</v>
+        <v>5</v>
       </c>
       <c r="AA24" t="n">
-        <v>1</v>
+        <v>-152</v>
       </c>
       <c r="AB24" t="n">
-        <v>6.54</v>
+        <v>-6.5</v>
       </c>
       <c r="AC24" t="n">
-        <v>14.8</v>
+        <v>9.24</v>
       </c>
       <c r="AD24" t="n">
-        <v>0.11</v>
+        <v>2.23</v>
       </c>
       <c r="AE24" t="b">
         <v>1</v>
       </c>
       <c r="AF24" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="AG24" t="n">
-        <v>227.44</v>
+        <v>594.08</v>
       </c>
       <c r="AH24" t="n">
-        <v>205</v>
+        <v>547.55</v>
       </c>
       <c r="AI24" t="n">
-        <v>37.8</v>
+        <v>29.2</v>
       </c>
       <c r="AJ24" t="n">
-        <v>234.3657360406091</v>
+        <v>593.6235208886742</v>
       </c>
       <c r="AK24" t="n">
-        <v>-1.5</v>
+        <v>8.9</v>
       </c>
       <c r="AL24" t="inlineStr">
         <is>
-          <t>Fresh</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="AM24" t="inlineStr">
         <is>
-          <t>Early Accumulation</t>
+          <t>Confirmed Accumulation</t>
         </is>
       </c>
       <c r="AN24" t="inlineStr">
         <is>
-          <t>Early Accumulation</t>
+          <t>Confirmed Accumulation</t>
         </is>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>21-09-2026</t>
+          <t>28-08-2026</t>
         </is>
       </c>
       <c r="AP24" t="inlineStr">
         <is>
-          <t>22-09-2026</t>
+          <t>11-09-2026</t>
         </is>
       </c>
       <c r="AQ24" t="n">
+        <v>14</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>27</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>13</v>
+      </c>
+      <c r="AT24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU24" t="n">
         <v>1</v>
       </c>
-      <c r="AR24" t="n">
+      <c r="AV24" t="n">
         <v>3</v>
       </c>
-      <c r="AS24" t="n">
-        <v>2</v>
-      </c>
-      <c r="AT24" t="n">
-        <v>2</v>
-      </c>
-      <c r="AU24" t="n">
-        <v>2</v>
-      </c>
-      <c r="AV24" t="n">
-        <v>2</v>
-      </c>
       <c r="AW24" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AX24" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AY24" t="n">
-        <v>2770203</v>
+        <v>0</v>
       </c>
       <c r="AZ24" t="n">
-        <v>2770203</v>
+        <v>322003</v>
       </c>
       <c r="BA24" t="n">
-        <v>2770203</v>
+        <v>2458195</v>
       </c>
       <c r="BB24" t="n">
-        <v>2770203</v>
+        <v>2458195</v>
       </c>
       <c r="BC24" t="n">
-        <v>2770203</v>
+        <v>2458195</v>
       </c>
       <c r="BD24" t="n">
         <v>0</v>
@@ -6163,19 +6161,19 @@
         <v>0</v>
       </c>
       <c r="BN24" t="n">
-        <v>2770203</v>
+        <v>0</v>
       </c>
       <c r="BO24" t="n">
-        <v>2770203</v>
+        <v>2458195</v>
       </c>
       <c r="BP24" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BQ24" t="n">
         <v>0</v>
       </c>
       <c r="BR24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -6413,12 +6411,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>SGIL</t>
+          <t>JAYAGROGN</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>SYNERGY GREEN INDUSTRIES LIMITED</t>
+          <t>Jayant Agro-Organics Limited</t>
         </is>
       </c>
       <c r="C26" t="n">
@@ -6430,40 +6428,40 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F26" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="G26" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="H26" t="n">
         <v>0</v>
       </c>
       <c r="I26" t="n">
-        <v>646.6</v>
+        <v>230.91</v>
       </c>
       <c r="J26" t="n">
-        <v>593.62</v>
+        <v>234.4</v>
       </c>
       <c r="K26" t="n">
-        <v>8.9</v>
+        <v>-1.5</v>
       </c>
       <c r="L26" t="n">
-        <v>74.02</v>
+        <v>67.13</v>
       </c>
       <c r="M26" t="n">
-        <v>0.25</v>
+        <v>0.3</v>
       </c>
       <c r="N26" t="n">
-        <v>2458195</v>
+        <v>2995877</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>2458195</v>
+        <v>2995877</v>
       </c>
       <c r="Q26" t="n">
         <v>0</v>
@@ -6481,94 +6479,96 @@
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>11-09-2026</t>
+          <t>23-09-2026</t>
         </is>
       </c>
       <c r="V26" t="n">
-        <v>0.025</v>
+        <v>0.043</v>
       </c>
       <c r="W26" t="n">
-        <v>1003</v>
-      </c>
-      <c r="X26" t="inlineStr"/>
+        <v>695</v>
+      </c>
+      <c r="X26" t="n">
+        <v>11.3</v>
+      </c>
       <c r="Y26" t="n">
-        <v>-2</v>
+        <v>-5</v>
       </c>
       <c r="Z26" t="n">
-        <v>5</v>
+        <v>32</v>
       </c>
       <c r="AA26" t="n">
-        <v>-152</v>
+        <v>1</v>
       </c>
       <c r="AB26" t="n">
-        <v>-6.5</v>
+        <v>6.54</v>
       </c>
       <c r="AC26" t="n">
-        <v>9.24</v>
+        <v>14.8</v>
       </c>
       <c r="AD26" t="n">
-        <v>2.23</v>
+        <v>0.11</v>
       </c>
       <c r="AE26" t="b">
         <v>1</v>
       </c>
       <c r="AF26" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="AG26" t="n">
-        <v>594.08</v>
+        <v>227.44</v>
       </c>
       <c r="AH26" t="n">
-        <v>547.55</v>
+        <v>205</v>
       </c>
       <c r="AI26" t="n">
-        <v>29.2</v>
+        <v>37.8</v>
       </c>
       <c r="AJ26" t="n">
-        <v>593.6235208886742</v>
+        <v>234.4008293560754</v>
       </c>
       <c r="AK26" t="n">
-        <v>8.9</v>
+        <v>-1.5</v>
       </c>
       <c r="AL26" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Fresh</t>
         </is>
       </c>
       <c r="AM26" t="inlineStr">
         <is>
-          <t>Confirmed Accumulation</t>
+          <t>Early Accumulation</t>
         </is>
       </c>
       <c r="AN26" t="inlineStr">
         <is>
-          <t>Confirmed Accumulation</t>
+          <t>Early Accumulation</t>
         </is>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>28-08-2026</t>
+          <t>21-09-2026</t>
         </is>
       </c>
       <c r="AP26" t="inlineStr">
         <is>
-          <t>11-09-2026</t>
+          <t>23-09-2026</t>
         </is>
       </c>
       <c r="AQ26" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="AR26" t="n">
-        <v>27</v>
+        <v>3</v>
       </c>
       <c r="AS26" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="AT26" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AU26" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AV26" t="n">
         <v>3</v>
@@ -6580,19 +6580,19 @@
         <v>3</v>
       </c>
       <c r="AY26" t="n">
-        <v>0</v>
+        <v>2995877</v>
       </c>
       <c r="AZ26" t="n">
-        <v>322003</v>
+        <v>2995877</v>
       </c>
       <c r="BA26" t="n">
-        <v>2458195</v>
+        <v>2995877</v>
       </c>
       <c r="BB26" t="n">
-        <v>2458195</v>
+        <v>2995877</v>
       </c>
       <c r="BC26" t="n">
-        <v>2458195</v>
+        <v>2995877</v>
       </c>
       <c r="BD26" t="n">
         <v>0</v>
@@ -6625,19 +6625,19 @@
         <v>0</v>
       </c>
       <c r="BN26" t="n">
-        <v>0</v>
+        <v>2995877</v>
       </c>
       <c r="BO26" t="n">
-        <v>2458195</v>
+        <v>2995877</v>
       </c>
       <c r="BP26" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BQ26" t="n">
         <v>0</v>
       </c>
       <c r="BR26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27">
@@ -6715,13 +6715,13 @@
         </is>
       </c>
       <c r="V27" t="n">
-        <v>0.462</v>
+        <v>0.454</v>
       </c>
       <c r="W27" t="n">
-        <v>401</v>
+        <v>408</v>
       </c>
       <c r="X27" t="n">
-        <v>37.2</v>
+        <v>37.9</v>
       </c>
       <c r="Y27" t="n">
         <v>21</v>
@@ -7414,7 +7414,7 @@
         <v>0.053</v>
       </c>
       <c r="W30" t="n">
-        <v>4999</v>
+        <v>5006</v>
       </c>
       <c r="X30" t="n">
         <v>32.6</v>
@@ -7643,13 +7643,13 @@
         </is>
       </c>
       <c r="V31" t="n">
-        <v>0.133</v>
+        <v>0.134</v>
       </c>
       <c r="W31" t="n">
-        <v>373</v>
+        <v>369</v>
       </c>
       <c r="X31" t="n">
-        <v>6.02</v>
+        <v>5.95</v>
       </c>
       <c r="Y31" t="n">
         <v>118</v>
@@ -7877,7 +7877,7 @@
         <v>370</v>
       </c>
       <c r="X32" t="n">
-        <v>1193</v>
+        <v>1194</v>
       </c>
       <c r="Y32" t="n">
         <v>-61</v>
@@ -8562,7 +8562,7 @@
         <v>0.008999999999999999</v>
       </c>
       <c r="W35" t="n">
-        <v>52493</v>
+        <v>52429</v>
       </c>
       <c r="X35" t="n">
         <v>44.4</v>
@@ -9026,10 +9026,10 @@
         <v>0.021</v>
       </c>
       <c r="W37" t="n">
-        <v>9503</v>
+        <v>9484</v>
       </c>
       <c r="X37" t="n">
-        <v>12.6</v>
+        <v>12.5</v>
       </c>
       <c r="Y37" t="n">
         <v>-12</v>
@@ -9722,10 +9722,10 @@
         <v>0</v>
       </c>
       <c r="W40" t="n">
-        <v>494</v>
+        <v>491</v>
       </c>
       <c r="X40" t="n">
-        <v>11.6</v>
+        <v>11.5</v>
       </c>
       <c r="Y40" t="n">
         <v>5</v>
@@ -10645,10 +10645,10 @@
         </is>
       </c>
       <c r="V44" t="n">
-        <v>0.225</v>
+        <v>0.224</v>
       </c>
       <c r="W44" t="n">
-        <v>1774</v>
+        <v>1780</v>
       </c>
       <c r="X44" t="n">
         <v>18.8</v>
@@ -11339,13 +11339,13 @@
         </is>
       </c>
       <c r="V47" t="n">
-        <v>0.354</v>
+        <v>0.357</v>
       </c>
       <c r="W47" t="n">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="X47" t="n">
-        <v>97.8</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="Y47" t="n">
         <v>246</v>
@@ -12038,7 +12038,7 @@
         <v>0</v>
       </c>
       <c r="W50" t="n">
-        <v>8892</v>
+        <v>8887</v>
       </c>
       <c r="X50" t="n">
         <v>15.1</v>
@@ -12270,10 +12270,10 @@
         <v>0</v>
       </c>
       <c r="W51" t="n">
-        <v>117949</v>
+        <v>118337</v>
       </c>
       <c r="X51" t="n">
-        <v>34</v>
+        <v>34.1</v>
       </c>
       <c r="Y51" t="n">
         <v>18</v>
@@ -12734,10 +12734,10 @@
         <v>0.083</v>
       </c>
       <c r="W53" t="n">
-        <v>1654</v>
+        <v>1655</v>
       </c>
       <c r="X53" t="n">
-        <v>29.8</v>
+        <v>29.9</v>
       </c>
       <c r="Y53" t="n">
         <v>39</v>
@@ -13010,23 +13010,23 @@
         <v>998.35</v>
       </c>
       <c r="D3" t="n">
-        <v>776.36</v>
+        <v>782.48</v>
       </c>
       <c r="E3" t="n">
-        <v>28.6</v>
+        <v>27.6</v>
       </c>
       <c r="F3" t="n">
         <v>61.71</v>
       </c>
       <c r="G3" t="n">
-        <v>2.78</v>
+        <v>2.88</v>
       </c>
       <c r="H3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>21-09-2026</t>
+          <t>22-09-2026</t>
         </is>
       </c>
     </row>
@@ -13593,70 +13593,70 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>AFFORDABLE</t>
+          <t>TAINWALCHM</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>AFFORDABLE ROBOTIC &amp; AUTOMATION LIMITED</t>
+          <t>TAINWALA CHEMICALS AND PLASTICS (INDIA) LIMITED</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>177.35</v>
+        <v>216.79</v>
       </c>
       <c r="D20" t="n">
-        <v>166.77</v>
+        <v>210</v>
       </c>
       <c r="E20" t="n">
-        <v>6.3</v>
+        <v>3.2</v>
       </c>
       <c r="F20" t="n">
-        <v>61.48</v>
+        <v>67.04000000000001</v>
       </c>
       <c r="G20" t="n">
-        <v>0.4</v>
+        <v>0.59</v>
       </c>
       <c r="H20" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>18-09-2026</t>
+          <t>17-09-2026</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>TAINWALCHM</t>
+          <t>AFFORDABLE</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>TAINWALA CHEMICALS AND PLASTICS (INDIA) LIMITED</t>
+          <t>AFFORDABLE ROBOTIC &amp; AUTOMATION LIMITED</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>216.79</v>
+        <v>177.35</v>
       </c>
       <c r="D21" t="n">
-        <v>210</v>
+        <v>169.88</v>
       </c>
       <c r="E21" t="n">
-        <v>3.2</v>
+        <v>4.4</v>
       </c>
       <c r="F21" t="n">
-        <v>67.04000000000001</v>
+        <v>61.48</v>
       </c>
       <c r="G21" t="n">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="H21" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>17-09-2026</t>
+          <t>23-09-2026</t>
         </is>
       </c>
     </row>
@@ -13733,35 +13733,35 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>JAYAGROGN</t>
+          <t>SGIL</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Jayant Agro-Organics Limited</t>
+          <t>SYNERGY GREEN INDUSTRIES LIMITED</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>230.91</v>
+        <v>646.6</v>
       </c>
       <c r="D24" t="n">
-        <v>234.37</v>
+        <v>593.62</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.5</v>
+        <v>8.9</v>
       </c>
       <c r="F24" t="n">
-        <v>67.13</v>
+        <v>74.02</v>
       </c>
       <c r="G24" t="n">
-        <v>0.28</v>
+        <v>0.25</v>
       </c>
       <c r="H24" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>22-09-2026</t>
+          <t>11-09-2026</t>
         </is>
       </c>
     </row>
@@ -13803,35 +13803,35 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>SGIL</t>
+          <t>JAYAGROGN</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>SYNERGY GREEN INDUSTRIES LIMITED</t>
+          <t>Jayant Agro-Organics Limited</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>646.6</v>
+        <v>230.91</v>
       </c>
       <c r="D26" t="n">
-        <v>593.62</v>
+        <v>234.4</v>
       </c>
       <c r="E26" t="n">
-        <v>8.9</v>
+        <v>-1.5</v>
       </c>
       <c r="F26" t="n">
-        <v>74.02</v>
+        <v>67.13</v>
       </c>
       <c r="G26" t="n">
-        <v>0.25</v>
+        <v>0.3</v>
       </c>
       <c r="H26" t="n">
         <v>3</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>11-09-2026</t>
+          <t>23-09-2026</t>
         </is>
       </c>
     </row>
